--- a/Images_BGA/Results/Reports/PCBA2_03__inspection_report.xlsx
+++ b/Images_BGA/Results/Reports/PCBA2_03__inspection_report.xlsx
@@ -632,16 +632,16 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="D5">
-        <v>835</v>
+        <v>853</v>
       </c>
       <c r="E5">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F5">
-        <v>5281.02</v>
+        <v>6082.12</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>1425</v>
+        <v>1433</v>
       </c>
       <c r="D6">
-        <v>836</v>
+        <v>848</v>
       </c>
       <c r="E6">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="F6">
-        <v>5026.55</v>
+        <v>6939.78</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>1.7706</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>1.7706</v>
+        <v>0</v>
       </c>
       <c r="L6" t="s">
         <v>15</v>
@@ -808,31 +808,31 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>1291</v>
+        <v>1285</v>
       </c>
       <c r="D9">
-        <v>837</v>
+        <v>851</v>
       </c>
       <c r="E9">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="F9">
-        <v>5281.02</v>
+        <v>6939.78</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>612</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>564</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>8.8187</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>8.1271</v>
       </c>
       <c r="L9" t="s">
         <v>15</v>
@@ -940,31 +940,31 @@
         <v>11</v>
       </c>
       <c r="C12">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="D12">
-        <v>838</v>
+        <v>856</v>
       </c>
       <c r="E12">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F12">
-        <v>5541.77</v>
+        <v>6939.78</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>0.4467</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>0.4467</v>
       </c>
       <c r="L12" t="s">
         <v>15</v>
@@ -984,31 +984,31 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="D13">
         <v>839</v>
       </c>
       <c r="E13">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F13">
-        <v>4778.36</v>
+        <v>4300.84</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="I13">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J13">
-        <v>2.5532</v>
+        <v>2.9064</v>
       </c>
       <c r="K13">
-        <v>1.6951</v>
+        <v>1.9531</v>
       </c>
       <c r="L13" t="s">
         <v>15</v>
@@ -1028,31 +1028,31 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="D14">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E14">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F14">
-        <v>5281.02</v>
+        <v>4778.36</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I14">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J14">
-        <v>1.8936</v>
+        <v>2.1765</v>
       </c>
       <c r="K14">
-        <v>1.8936</v>
+        <v>2.1765</v>
       </c>
       <c r="L14" t="s">
         <v>15</v>
@@ -1072,31 +1072,31 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>898</v>
+        <v>887</v>
       </c>
       <c r="D15">
-        <v>839</v>
+        <v>855</v>
       </c>
       <c r="E15">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="F15">
-        <v>5281.02</v>
+        <v>6939.78</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>767</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>767</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>11.0522</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>11.0522</v>
       </c>
       <c r="L15" t="s">
         <v>15</v>
@@ -1292,31 +1292,31 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="D20">
-        <v>926</v>
+        <v>908</v>
       </c>
       <c r="E20">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F20">
-        <v>5808.8</v>
+        <v>6361.73</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="I20">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J20">
-        <v>0.5337</v>
+        <v>0.2987</v>
       </c>
       <c r="K20">
-        <v>0.5337</v>
+        <v>0.2987</v>
       </c>
       <c r="L20" t="s">
         <v>15</v>
@@ -1427,28 +1427,28 @@
         <v>1160</v>
       </c>
       <c r="D23">
-        <v>928</v>
+        <v>910</v>
       </c>
       <c r="E23">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F23">
-        <v>5541.77</v>
+        <v>6082.12</v>
       </c>
       <c r="G23">
         <v>3</v>
       </c>
       <c r="H23">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="I23">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J23">
-        <v>3.0857</v>
+        <v>3.1568</v>
       </c>
       <c r="K23">
-        <v>1.9308</v>
+        <v>1.6935</v>
       </c>
       <c r="L23" t="s">
         <v>15</v>
@@ -1864,31 +1864,31 @@
         <v>32</v>
       </c>
       <c r="C33">
-        <v>1564</v>
+        <v>1557</v>
       </c>
       <c r="D33">
-        <v>933</v>
+        <v>948</v>
       </c>
       <c r="E33">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F33">
-        <v>5281.02</v>
+        <v>6361.73</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
-        <v>50</v>
+        <v>233</v>
       </c>
       <c r="I33">
-        <v>50</v>
+        <v>233</v>
       </c>
       <c r="J33">
-        <v>0.9468</v>
+        <v>3.6625</v>
       </c>
       <c r="K33">
-        <v>0.9468</v>
+        <v>3.6625</v>
       </c>
       <c r="L33" t="s">
         <v>15</v>
@@ -1908,31 +1908,31 @@
         <v>33</v>
       </c>
       <c r="C34">
-        <v>1566</v>
+        <v>1558</v>
       </c>
       <c r="D34">
-        <v>1012</v>
+        <v>995</v>
       </c>
       <c r="E34">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F34">
-        <v>4778.36</v>
+        <v>6082.12</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="I34">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="J34">
-        <v>2.2811</v>
+        <v>1.562</v>
       </c>
       <c r="K34">
-        <v>2.2811</v>
+        <v>1.562</v>
       </c>
       <c r="L34" t="s">
         <v>15</v>
@@ -1952,16 +1952,16 @@
         <v>34</v>
       </c>
       <c r="C35">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="D35">
-        <v>1016</v>
+        <v>999</v>
       </c>
       <c r="E35">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F35">
-        <v>5281.02</v>
+        <v>6082.12</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -1996,31 +1996,31 @@
         <v>35</v>
       </c>
       <c r="C36">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="D36">
-        <v>1017</v>
+        <v>1036</v>
       </c>
       <c r="E36">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F36">
-        <v>6082.12</v>
+        <v>6361.73</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36">
-        <v>196</v>
+        <v>125</v>
       </c>
       <c r="I36">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="J36">
-        <v>3.2226</v>
+        <v>1.9649</v>
       </c>
       <c r="K36">
-        <v>2.2525</v>
+        <v>1.9649</v>
       </c>
       <c r="L36" t="s">
         <v>15</v>
@@ -2084,31 +2084,31 @@
         <v>37</v>
       </c>
       <c r="C38">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D38">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E38">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F38">
-        <v>4300.84</v>
+        <v>3848.45</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>3.274</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>3.274</v>
       </c>
       <c r="L38" t="s">
         <v>15</v>
@@ -2128,31 +2128,31 @@
         <v>38</v>
       </c>
       <c r="C39">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="D39">
-        <v>1019</v>
+        <v>1001</v>
       </c>
       <c r="E39">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F39">
-        <v>5808.8</v>
+        <v>6082.12</v>
       </c>
       <c r="G39">
         <v>2</v>
       </c>
       <c r="H39">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I39">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J39">
-        <v>1.6699</v>
+        <v>1.6113</v>
       </c>
       <c r="K39">
-        <v>1.0846</v>
+        <v>0.9701</v>
       </c>
       <c r="L39" t="s">
         <v>15</v>
@@ -2392,7 +2392,7 @@
         <v>44</v>
       </c>
       <c r="C45">
-        <v>2176</v>
+        <v>2229</v>
       </c>
       <c r="D45">
         <v>1021</v>
@@ -2404,19 +2404,19 @@
         <v>6939.78</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>0.7925</v>
       </c>
       <c r="K45">
-        <v>0</v>
+        <v>0.7925</v>
       </c>
       <c r="L45" t="s">
         <v>15</v>
@@ -2612,31 +2612,31 @@
         <v>49</v>
       </c>
       <c r="C50">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="D50">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="E50">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F50">
-        <v>5808.8</v>
+        <v>6647.61</v>
       </c>
       <c r="G50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H50">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="I50">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="J50">
-        <v>1.6527</v>
+        <v>1.7299</v>
       </c>
       <c r="K50">
-        <v>0.9985000000000001</v>
+        <v>0.7822</v>
       </c>
       <c r="L50" t="s">
         <v>15</v>
@@ -2656,16 +2656,16 @@
         <v>50</v>
       </c>
       <c r="C51">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="D51">
-        <v>1111</v>
+        <v>1092</v>
       </c>
       <c r="E51">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F51">
-        <v>6082.12</v>
+        <v>6361.73</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -2677,10 +2677,10 @@
         <v>30</v>
       </c>
       <c r="J51">
-        <v>0.4932</v>
+        <v>0.4716</v>
       </c>
       <c r="K51">
-        <v>0.4932</v>
+        <v>0.4716</v>
       </c>
       <c r="L51" t="s">
         <v>15</v>
@@ -2700,31 +2700,31 @@
         <v>51</v>
       </c>
       <c r="C52">
-        <v>1431</v>
+        <v>1428</v>
       </c>
       <c r="D52">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="E52">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F52">
-        <v>5541.77</v>
+        <v>5026.55</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="I52">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J52">
-        <v>1.2992</v>
+        <v>2.3276</v>
       </c>
       <c r="K52">
-        <v>1.2992</v>
+        <v>1.4523</v>
       </c>
       <c r="L52" t="s">
         <v>15</v>
@@ -2744,31 +2744,31 @@
         <v>52</v>
       </c>
       <c r="C53">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="D53">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="E53">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F53">
-        <v>5281.02</v>
+        <v>4778.36</v>
       </c>
       <c r="G53">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H53">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I53">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="J53">
-        <v>2.9729</v>
+        <v>3.181</v>
       </c>
       <c r="K53">
-        <v>1.193</v>
+        <v>1.3812</v>
       </c>
       <c r="L53" t="s">
         <v>15</v>
@@ -2788,31 +2788,31 @@
         <v>53</v>
       </c>
       <c r="C54">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="D54">
-        <v>1114</v>
+        <v>1096</v>
       </c>
       <c r="E54">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F54">
-        <v>6082.12</v>
+        <v>6647.61</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="I54">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J54">
-        <v>2.2854</v>
+        <v>1.6848</v>
       </c>
       <c r="K54">
-        <v>1.2002</v>
+        <v>1.0831</v>
       </c>
       <c r="L54" t="s">
         <v>15</v>
@@ -2876,16 +2876,16 @@
         <v>55</v>
       </c>
       <c r="C56">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="D56">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="E56">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F56">
-        <v>5281.02</v>
+        <v>5026.55</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -2897,10 +2897,10 @@
         <v>86</v>
       </c>
       <c r="J56">
-        <v>1.6285</v>
+        <v>1.7109</v>
       </c>
       <c r="K56">
-        <v>1.6285</v>
+        <v>1.7109</v>
       </c>
       <c r="L56" t="s">
         <v>15</v>
@@ -2920,31 +2920,31 @@
         <v>56</v>
       </c>
       <c r="C57">
-        <v>1569</v>
+        <v>1561</v>
       </c>
       <c r="D57">
-        <v>1115</v>
+        <v>1127</v>
       </c>
       <c r="E57">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="F57">
-        <v>4778.36</v>
+        <v>6647.61</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
       <c r="H57">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I57">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J57">
-        <v>1.6533</v>
+        <v>1.0681</v>
       </c>
       <c r="K57">
-        <v>1.6533</v>
+        <v>1.0681</v>
       </c>
       <c r="L57" t="s">
         <v>15</v>
@@ -2964,16 +2964,16 @@
         <v>57</v>
       </c>
       <c r="C58">
-        <v>2178</v>
+        <v>2111</v>
       </c>
       <c r="D58">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="E58">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F58">
-        <v>6939.78</v>
+        <v>6647.61</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -3052,31 +3052,31 @@
         <v>59</v>
       </c>
       <c r="C60">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D60">
         <v>1116</v>
       </c>
       <c r="E60">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F60">
-        <v>5281.02</v>
+        <v>4536.46</v>
       </c>
       <c r="G60">
         <v>2</v>
       </c>
       <c r="H60">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="I60">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J60">
-        <v>1.9125</v>
+        <v>2.4468</v>
       </c>
       <c r="K60">
-        <v>1.4581</v>
+        <v>1.7414</v>
       </c>
       <c r="L60" t="s">
         <v>15</v>
@@ -3140,31 +3140,31 @@
         <v>61</v>
       </c>
       <c r="C62">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="D62">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="E62">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F62">
-        <v>5541.77</v>
+        <v>4778.36</v>
       </c>
       <c r="G62">
         <v>2</v>
       </c>
       <c r="H62">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I62">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J62">
-        <v>1.4075</v>
+        <v>1.8207</v>
       </c>
       <c r="K62">
-        <v>1.0466</v>
+        <v>1.3394</v>
       </c>
       <c r="L62" t="s">
         <v>15</v>
@@ -3231,28 +3231,28 @@
         <v>486</v>
       </c>
       <c r="D64">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="E64">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F64">
-        <v>5026.55</v>
+        <v>4300.84</v>
       </c>
       <c r="G64">
         <v>1</v>
       </c>
       <c r="H64">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I64">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J64">
-        <v>0.6764</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="K64">
-        <v>0.6764</v>
+        <v>0.9068000000000001</v>
       </c>
       <c r="L64" t="s">
         <v>15</v>
@@ -3316,16 +3316,16 @@
         <v>65</v>
       </c>
       <c r="C66">
-        <v>1977</v>
+        <v>1974</v>
       </c>
       <c r="D66">
-        <v>1205</v>
+        <v>1186</v>
       </c>
       <c r="E66">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F66">
-        <v>6082.12</v>
+        <v>6361.73</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -3337,10 +3337,10 @@
         <v>132</v>
       </c>
       <c r="J66">
-        <v>2.1703</v>
+        <v>2.0749</v>
       </c>
       <c r="K66">
-        <v>2.1703</v>
+        <v>2.0749</v>
       </c>
       <c r="L66" t="s">
         <v>15</v>
@@ -3360,16 +3360,16 @@
         <v>66</v>
       </c>
       <c r="C67">
-        <v>2113</v>
+        <v>2110</v>
       </c>
       <c r="D67">
-        <v>1205</v>
+        <v>1186</v>
       </c>
       <c r="E67">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F67">
-        <v>6082.12</v>
+        <v>6361.73</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -3407,28 +3407,28 @@
         <v>1839</v>
       </c>
       <c r="D68">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="E68">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F68">
-        <v>5541.77</v>
+        <v>4536.46</v>
       </c>
       <c r="G68">
         <v>2</v>
       </c>
       <c r="H68">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I68">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="J68">
-        <v>1.7143</v>
+        <v>2.0721</v>
       </c>
       <c r="K68">
-        <v>1.1729</v>
+        <v>1.5871</v>
       </c>
       <c r="L68" t="s">
         <v>15</v>
@@ -3448,31 +3448,31 @@
         <v>68</v>
       </c>
       <c r="C69">
-        <v>1571</v>
+        <v>1562</v>
       </c>
       <c r="D69">
-        <v>1207</v>
+        <v>1193</v>
       </c>
       <c r="E69">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F69">
-        <v>5541.77</v>
+        <v>6647.61</v>
       </c>
       <c r="G69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H69">
-        <v>108</v>
+        <v>190</v>
       </c>
       <c r="I69">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="J69">
-        <v>1.9488</v>
+        <v>2.8582</v>
       </c>
       <c r="K69">
-        <v>1.0286</v>
+        <v>1.3087</v>
       </c>
       <c r="L69" t="s">
         <v>15</v>
@@ -3495,28 +3495,28 @@
         <v>1702</v>
       </c>
       <c r="D70">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="E70">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F70">
-        <v>5808.8</v>
+        <v>5026.55</v>
       </c>
       <c r="G70">
         <v>1</v>
       </c>
       <c r="H70">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I70">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J70">
-        <v>1.2223</v>
+        <v>1.4921</v>
       </c>
       <c r="K70">
-        <v>1.2223</v>
+        <v>1.4921</v>
       </c>
       <c r="L70" t="s">
         <v>15</v>
@@ -3583,28 +3583,28 @@
         <v>1431</v>
       </c>
       <c r="D72">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="E72">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F72">
-        <v>5541.77</v>
+        <v>5281.02</v>
       </c>
       <c r="G72">
         <v>1</v>
       </c>
       <c r="H72">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I72">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J72">
-        <v>0.7579</v>
+        <v>0.8521</v>
       </c>
       <c r="K72">
-        <v>0.7579</v>
+        <v>0.8521</v>
       </c>
       <c r="L72" t="s">
         <v>15</v>
@@ -3624,16 +3624,16 @@
         <v>72</v>
       </c>
       <c r="C73">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="D73">
         <v>1209</v>
       </c>
       <c r="E73">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F73">
-        <v>5541.77</v>
+        <v>4778.36</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -3756,31 +3756,31 @@
         <v>75</v>
       </c>
       <c r="C76">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D76">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="E76">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F76">
-        <v>5281.02</v>
+        <v>4778.36</v>
       </c>
       <c r="G76">
         <v>1</v>
       </c>
       <c r="H76">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="I76">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J76">
-        <v>1.3255</v>
+        <v>1.5905</v>
       </c>
       <c r="K76">
-        <v>1.3255</v>
+        <v>1.5905</v>
       </c>
       <c r="L76" t="s">
         <v>15</v>
@@ -3800,31 +3800,31 @@
         <v>76</v>
       </c>
       <c r="C77">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="D77">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="E77">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F77">
-        <v>5541.77</v>
+        <v>6647.61</v>
       </c>
       <c r="G77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H77">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="I77">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J77">
-        <v>1.2631</v>
+        <v>0.7371</v>
       </c>
       <c r="K77">
-        <v>0.4872</v>
+        <v>0.3911</v>
       </c>
       <c r="L77" t="s">
         <v>15</v>
@@ -4064,31 +4064,31 @@
         <v>82</v>
       </c>
       <c r="C83">
-        <v>1573</v>
+        <v>1567</v>
       </c>
       <c r="D83">
-        <v>1304</v>
+        <v>1309</v>
       </c>
       <c r="E83">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F83">
-        <v>5026.55</v>
+        <v>5541.77</v>
       </c>
       <c r="G83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H83">
-        <v>254</v>
+        <v>166</v>
       </c>
       <c r="I83">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="J83">
-        <v>5.0532</v>
+        <v>2.9954</v>
       </c>
       <c r="K83">
-        <v>2.7454</v>
+        <v>1.7684</v>
       </c>
       <c r="L83" t="s">
         <v>15</v>
@@ -4240,31 +4240,31 @@
         <v>86</v>
       </c>
       <c r="C87">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="D87">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="E87">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F87">
-        <v>5808.8</v>
+        <v>5541.77</v>
       </c>
       <c r="G87">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H87">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="I87">
         <v>116</v>
       </c>
       <c r="J87">
-        <v>6.0253</v>
+        <v>5.5939</v>
       </c>
       <c r="K87">
-        <v>1.997</v>
+        <v>2.0932</v>
       </c>
       <c r="L87" t="s">
         <v>15</v>
@@ -4284,31 +4284,31 @@
         <v>87</v>
       </c>
       <c r="C88">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D88">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="E88">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F88">
-        <v>5281.02</v>
+        <v>4778.36</v>
       </c>
       <c r="G88">
         <v>1</v>
       </c>
       <c r="H88">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="I88">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J88">
-        <v>2.0072</v>
+        <v>2.2602</v>
       </c>
       <c r="K88">
-        <v>2.0072</v>
+        <v>2.2602</v>
       </c>
       <c r="L88" t="s">
         <v>15</v>
@@ -4328,31 +4328,31 @@
         <v>88</v>
       </c>
       <c r="C89">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D89">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="E89">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F89">
-        <v>5541.77</v>
+        <v>5281.02</v>
       </c>
       <c r="G89">
         <v>1</v>
       </c>
       <c r="H89">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I89">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="J89">
-        <v>2.6706</v>
+        <v>2.8782</v>
       </c>
       <c r="K89">
-        <v>2.6706</v>
+        <v>2.8782</v>
       </c>
       <c r="L89" t="s">
         <v>15</v>
@@ -4460,10 +4460,10 @@
         <v>91</v>
       </c>
       <c r="C92">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="D92">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="E92">
         <v>84</v>
@@ -4472,16 +4472,16 @@
         <v>5541.77</v>
       </c>
       <c r="G92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H92">
-        <v>190</v>
+        <v>226</v>
       </c>
       <c r="I92">
         <v>106</v>
       </c>
       <c r="J92">
-        <v>3.4285</v>
+        <v>4.0781</v>
       </c>
       <c r="K92">
         <v>1.9127</v>
@@ -4592,31 +4592,31 @@
         <v>94</v>
       </c>
       <c r="C95">
-        <v>862</v>
+        <v>884</v>
       </c>
       <c r="D95">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="E95">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F95">
-        <v>6939.78</v>
+        <v>5281.02</v>
       </c>
       <c r="G95">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H95">
-        <v>375</v>
+        <v>261</v>
       </c>
       <c r="I95">
-        <v>206</v>
+        <v>137</v>
       </c>
       <c r="J95">
-        <v>5.4036</v>
+        <v>4.9422</v>
       </c>
       <c r="K95">
-        <v>2.9684</v>
+        <v>2.5942</v>
       </c>
       <c r="L95" t="s">
         <v>15</v>
@@ -4680,31 +4680,31 @@
         <v>96</v>
       </c>
       <c r="C97">
-        <v>2275</v>
+        <v>2271</v>
       </c>
       <c r="D97">
-        <v>1394</v>
+        <v>1379</v>
       </c>
       <c r="E97">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F97">
-        <v>5541.77</v>
+        <v>6939.78</v>
       </c>
       <c r="G97">
         <v>1</v>
       </c>
       <c r="H97">
-        <v>21</v>
+        <v>691</v>
       </c>
       <c r="I97">
-        <v>21</v>
+        <v>691</v>
       </c>
       <c r="J97">
-        <v>0.3789</v>
+        <v>9.957100000000001</v>
       </c>
       <c r="K97">
-        <v>0.3789</v>
+        <v>9.957100000000001</v>
       </c>
       <c r="L97" t="s">
         <v>15</v>
@@ -4856,16 +4856,16 @@
         <v>100</v>
       </c>
       <c r="C101">
-        <v>1576</v>
+        <v>1573</v>
       </c>
       <c r="D101">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="E101">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F101">
-        <v>5541.77</v>
+        <v>5026.55</v>
       </c>
       <c r="G101">
         <v>1</v>
@@ -4877,10 +4877,10 @@
         <v>47</v>
       </c>
       <c r="J101">
-        <v>0.8481</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="K101">
-        <v>0.8481</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="L101" t="s">
         <v>15</v>
@@ -4944,16 +4944,16 @@
         <v>102</v>
       </c>
       <c r="C103">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="D103">
         <v>1407</v>
       </c>
       <c r="E103">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F103">
-        <v>5281.02</v>
+        <v>5026.55</v>
       </c>
       <c r="G103">
         <v>2</v>
@@ -4965,10 +4965,10 @@
         <v>81</v>
       </c>
       <c r="J103">
-        <v>2.064</v>
+        <v>2.1685</v>
       </c>
       <c r="K103">
-        <v>1.5338</v>
+        <v>1.6114</v>
       </c>
       <c r="L103" t="s">
         <v>15</v>
@@ -4988,16 +4988,16 @@
         <v>103</v>
       </c>
       <c r="C104">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D104">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="E104">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F104">
-        <v>5281.02</v>
+        <v>5808.8</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -5032,31 +5032,31 @@
         <v>104</v>
       </c>
       <c r="C105">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D105">
         <v>1409</v>
       </c>
       <c r="E105">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F105">
-        <v>5281.02</v>
+        <v>4778.36</v>
       </c>
       <c r="G105">
         <v>2</v>
       </c>
       <c r="H105">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I105">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="J105">
-        <v>1.7042</v>
+        <v>1.6114</v>
       </c>
       <c r="K105">
-        <v>1.1551</v>
+        <v>0.9417</v>
       </c>
       <c r="L105" t="s">
         <v>15</v>
@@ -5208,31 +5208,31 @@
         <v>108</v>
       </c>
       <c r="C109">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="D109">
-        <v>1411</v>
+        <v>1408</v>
       </c>
       <c r="E109">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F109">
-        <v>6361.73</v>
+        <v>5026.55</v>
       </c>
       <c r="G109">
         <v>2</v>
       </c>
       <c r="H109">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="I109">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J109">
-        <v>2.4679</v>
+        <v>3.2826</v>
       </c>
       <c r="K109">
-        <v>1.3676</v>
+        <v>1.7706</v>
       </c>
       <c r="L109" t="s">
         <v>15</v>
@@ -5340,31 +5340,31 @@
         <v>111</v>
       </c>
       <c r="C112">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="D112">
-        <v>1415</v>
+        <v>1409</v>
       </c>
       <c r="E112">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="F112">
-        <v>6939.78</v>
+        <v>5026.55</v>
       </c>
       <c r="G112">
         <v>1</v>
       </c>
       <c r="H112">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I112">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J112">
-        <v>0.9799</v>
+        <v>1.4125</v>
       </c>
       <c r="K112">
-        <v>0.9799</v>
+        <v>1.4125</v>
       </c>
       <c r="L112" t="s">
         <v>15</v>
@@ -5384,31 +5384,31 @@
         <v>112</v>
       </c>
       <c r="C113">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="D113">
         <v>1502</v>
       </c>
       <c r="E113">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F113">
-        <v>6082.12</v>
+        <v>5026.55</v>
       </c>
       <c r="G113">
         <v>2</v>
       </c>
       <c r="H113">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="I113">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="J113">
-        <v>1.3482</v>
+        <v>1.4125</v>
       </c>
       <c r="K113">
-        <v>0.7399</v>
+        <v>0.8157</v>
       </c>
       <c r="L113" t="s">
         <v>15</v>
@@ -5604,31 +5604,31 @@
         <v>117</v>
       </c>
       <c r="C118">
-        <v>1589</v>
+        <v>1573</v>
       </c>
       <c r="D118">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="E118">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F118">
-        <v>5281.02</v>
+        <v>6361.73</v>
       </c>
       <c r="G118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H118">
-        <v>103</v>
+        <v>49</v>
       </c>
       <c r="I118">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="J118">
-        <v>1.9504</v>
+        <v>0.7702</v>
       </c>
       <c r="K118">
-        <v>0.8142</v>
+        <v>0.4873</v>
       </c>
       <c r="L118" t="s">
         <v>15</v>
@@ -5695,13 +5695,13 @@
         <v>735</v>
       </c>
       <c r="D120">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="E120">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F120">
-        <v>5281.02</v>
+        <v>5026.55</v>
       </c>
       <c r="G120">
         <v>3</v>
@@ -5713,10 +5713,10 @@
         <v>45</v>
       </c>
       <c r="J120">
-        <v>1.9314</v>
+        <v>2.0292</v>
       </c>
       <c r="K120">
-        <v>0.8521</v>
+        <v>0.8952</v>
       </c>
       <c r="L120" t="s">
         <v>15</v>
@@ -5871,28 +5871,28 @@
         <v>454</v>
       </c>
       <c r="D124">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="E124">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F124">
-        <v>5541.77</v>
+        <v>5026.55</v>
       </c>
       <c r="G124">
         <v>1</v>
       </c>
       <c r="H124">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I124">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J124">
-        <v>0.415</v>
+        <v>0.4775</v>
       </c>
       <c r="K124">
-        <v>0.415</v>
+        <v>0.4775</v>
       </c>
       <c r="L124" t="s">
         <v>15</v>
@@ -5912,16 +5912,16 @@
         <v>124</v>
       </c>
       <c r="C125">
-        <v>862</v>
+        <v>878</v>
       </c>
       <c r="D125">
-        <v>1512</v>
+        <v>1510</v>
       </c>
       <c r="E125">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F125">
-        <v>6939.78</v>
+        <v>5281.02</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -6044,10 +6044,10 @@
         <v>127</v>
       </c>
       <c r="C128">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D128">
-        <v>1513</v>
+        <v>1516</v>
       </c>
       <c r="E128">
         <v>94</v>
@@ -6088,16 +6088,16 @@
         <v>128</v>
       </c>
       <c r="C129">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="D129">
-        <v>1602</v>
+        <v>1616</v>
       </c>
       <c r="E129">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F129">
-        <v>6939.78</v>
+        <v>5541.77</v>
       </c>
       <c r="G129">
         <v>0</v>
@@ -6223,28 +6223,28 @@
         <v>2010</v>
       </c>
       <c r="D132">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="E132">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F132">
-        <v>6082.12</v>
+        <v>5026.55</v>
       </c>
       <c r="G132">
         <v>2</v>
       </c>
       <c r="H132">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="I132">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="J132">
-        <v>3.2061</v>
+        <v>4.4364</v>
       </c>
       <c r="K132">
-        <v>2.68</v>
+        <v>3.581</v>
       </c>
       <c r="L132" t="s">
         <v>15</v>
@@ -6396,31 +6396,31 @@
         <v>135</v>
       </c>
       <c r="C136">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="D136">
-        <v>1615</v>
+        <v>1607</v>
       </c>
       <c r="E136">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F136">
-        <v>5808.8</v>
+        <v>6361.73</v>
       </c>
       <c r="G136">
         <v>1</v>
       </c>
       <c r="H136">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I136">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="J136">
-        <v>0.6197</v>
+        <v>0.4873</v>
       </c>
       <c r="K136">
-        <v>0.6197</v>
+        <v>0.4873</v>
       </c>
       <c r="L136" t="s">
         <v>15</v>
@@ -6572,31 +6572,31 @@
         <v>139</v>
       </c>
       <c r="C140">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="D140">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="E140">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F140">
-        <v>6647.61</v>
+        <v>5808.8</v>
       </c>
       <c r="G140">
         <v>2</v>
       </c>
       <c r="H140">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="I140">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="J140">
-        <v>0.7822</v>
+        <v>1.0157</v>
       </c>
       <c r="K140">
-        <v>0.5265</v>
+        <v>0.7058</v>
       </c>
       <c r="L140" t="s">
         <v>15</v>
@@ -6704,31 +6704,31 @@
         <v>142</v>
       </c>
       <c r="C143">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="D143">
         <v>1616</v>
       </c>
       <c r="E143">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F143">
-        <v>6361.73</v>
+        <v>5541.77</v>
       </c>
       <c r="G143">
         <v>2</v>
       </c>
       <c r="H143">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="I143">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="J143">
-        <v>1.1789</v>
+        <v>1.6782</v>
       </c>
       <c r="K143">
-        <v>0.613</v>
+        <v>0.9383</v>
       </c>
       <c r="L143" t="s">
         <v>15</v>
@@ -6748,31 +6748,31 @@
         <v>143</v>
       </c>
       <c r="C144">
-        <v>1597</v>
+        <v>1582</v>
       </c>
       <c r="D144">
-        <v>1619</v>
+        <v>1613</v>
       </c>
       <c r="E144">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F144">
-        <v>6939.78</v>
+        <v>5281.02</v>
       </c>
       <c r="G144">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H144">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="I144">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="J144">
-        <v>1.4986</v>
+        <v>2.7836</v>
       </c>
       <c r="K144">
-        <v>0.8069</v>
+        <v>1.193</v>
       </c>
       <c r="L144" t="s">
         <v>15</v>
@@ -6792,31 +6792,31 @@
         <v>144</v>
       </c>
       <c r="C145">
-        <v>1299</v>
+        <v>1293</v>
       </c>
       <c r="D145">
-        <v>1704</v>
+        <v>1721</v>
       </c>
       <c r="E145">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F145">
-        <v>6939.78</v>
+        <v>6647.61</v>
       </c>
       <c r="G145">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H145">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="I145">
         <v>18</v>
       </c>
       <c r="J145">
-        <v>0.5043</v>
+        <v>0.7672</v>
       </c>
       <c r="K145">
-        <v>0.2594</v>
+        <v>0.2708</v>
       </c>
       <c r="L145" t="s">
         <v>15</v>
@@ -6836,10 +6836,10 @@
         <v>145</v>
       </c>
       <c r="C146">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="D146">
-        <v>1714</v>
+        <v>1722</v>
       </c>
       <c r="E146">
         <v>94</v>
@@ -6848,16 +6848,16 @@
         <v>6939.78</v>
       </c>
       <c r="G146">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H146">
-        <v>385</v>
+        <v>292</v>
       </c>
       <c r="I146">
         <v>125</v>
       </c>
       <c r="J146">
-        <v>5.5477</v>
+        <v>4.2076</v>
       </c>
       <c r="K146">
         <v>1.8012</v>
@@ -6880,31 +6880,31 @@
         <v>146</v>
       </c>
       <c r="C147">
-        <v>1602</v>
+        <v>1589</v>
       </c>
       <c r="D147">
-        <v>1715</v>
+        <v>1719</v>
       </c>
       <c r="E147">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="F147">
-        <v>6939.78</v>
+        <v>5026.55</v>
       </c>
       <c r="G147">
         <v>3</v>
       </c>
       <c r="H147">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="I147">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J147">
-        <v>1.5995</v>
+        <v>2.3077</v>
       </c>
       <c r="K147">
-        <v>0.6627999999999999</v>
+        <v>1.0544</v>
       </c>
       <c r="L147" t="s">
         <v>15</v>
@@ -7015,28 +7015,28 @@
         <v>1872</v>
       </c>
       <c r="D150">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="E150">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F150">
-        <v>5281.02</v>
+        <v>5026.55</v>
       </c>
       <c r="G150">
         <v>3</v>
       </c>
       <c r="H150">
-        <v>203</v>
+        <v>182</v>
       </c>
       <c r="I150">
         <v>93</v>
       </c>
       <c r="J150">
-        <v>3.844</v>
+        <v>3.6208</v>
       </c>
       <c r="K150">
-        <v>1.761</v>
+        <v>1.8502</v>
       </c>
       <c r="L150" t="s">
         <v>15</v>
@@ -7103,7 +7103,7 @@
         <v>286</v>
       </c>
       <c r="D152">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="E152">
         <v>88</v>
@@ -7115,16 +7115,16 @@
         <v>2</v>
       </c>
       <c r="H152">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I152">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J152">
-        <v>0.7563</v>
+        <v>0.6905</v>
       </c>
       <c r="K152">
-        <v>0.4932</v>
+        <v>0.4275</v>
       </c>
       <c r="L152" t="s">
         <v>15</v>
@@ -7144,10 +7144,10 @@
         <v>152</v>
       </c>
       <c r="C153">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="D153">
-        <v>1718</v>
+        <v>1721</v>
       </c>
       <c r="E153">
         <v>82</v>
@@ -7232,31 +7232,31 @@
         <v>154</v>
       </c>
       <c r="C155">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D155">
-        <v>1721</v>
+        <v>1712</v>
       </c>
       <c r="E155">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F155">
-        <v>6361.73</v>
+        <v>6939.78</v>
       </c>
       <c r="G155">
         <v>2</v>
       </c>
       <c r="H155">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="I155">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="J155">
-        <v>1.3676</v>
+        <v>0.879</v>
       </c>
       <c r="K155">
-        <v>0.8174</v>
+        <v>0.4611</v>
       </c>
       <c r="L155" t="s">
         <v>15</v>
@@ -7279,13 +7279,13 @@
         <v>581</v>
       </c>
       <c r="D156">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="E156">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F156">
-        <v>5808.8</v>
+        <v>5541.77</v>
       </c>
       <c r="G156">
         <v>3</v>
@@ -7297,10 +7297,10 @@
         <v>81</v>
       </c>
       <c r="J156">
-        <v>3.3398</v>
+        <v>3.5007</v>
       </c>
       <c r="K156">
-        <v>1.3944</v>
+        <v>1.4616</v>
       </c>
       <c r="L156" t="s">
         <v>15</v>
@@ -7408,31 +7408,31 @@
         <v>158</v>
       </c>
       <c r="C159">
-        <v>1013</v>
+        <v>1022</v>
       </c>
       <c r="D159">
-        <v>1723</v>
+        <v>1730</v>
       </c>
       <c r="E159">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F159">
-        <v>6082.12</v>
+        <v>6939.78</v>
       </c>
       <c r="G159">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H159">
-        <v>163</v>
+        <v>99</v>
       </c>
       <c r="I159">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="J159">
-        <v>2.68</v>
+        <v>1.4266</v>
       </c>
       <c r="K159">
-        <v>0.8878</v>
+        <v>0.7349</v>
       </c>
       <c r="L159" t="s">
         <v>15</v>
@@ -7455,7 +7455,7 @@
         <v>1156</v>
       </c>
       <c r="D160">
-        <v>1729</v>
+        <v>1722</v>
       </c>
       <c r="E160">
         <v>94</v>
@@ -7540,7 +7540,7 @@
         <v>161</v>
       </c>
       <c r="C162">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="D162">
         <v>1825</v>
@@ -7584,31 +7584,31 @@
         <v>162</v>
       </c>
       <c r="C163">
-        <v>1590</v>
+        <v>1581</v>
       </c>
       <c r="D163">
-        <v>1826</v>
+        <v>1810</v>
       </c>
       <c r="E163">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F163">
-        <v>5541.77</v>
+        <v>6939.78</v>
       </c>
       <c r="G163">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H163">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="I163">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="J163">
-        <v>2.4902</v>
+        <v>1.2681</v>
       </c>
       <c r="K163">
-        <v>1.0466</v>
+        <v>0.7925</v>
       </c>
       <c r="L163" t="s">
         <v>15</v>
@@ -7672,31 +7672,31 @@
         <v>164</v>
       </c>
       <c r="C165">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="D165">
         <v>1826</v>
       </c>
       <c r="E165">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F165">
-        <v>5541.77</v>
+        <v>5026.55</v>
       </c>
       <c r="G165">
         <v>1</v>
       </c>
       <c r="H165">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I165">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J165">
-        <v>0.8300999999999999</v>
+        <v>0.9748</v>
       </c>
       <c r="K165">
-        <v>0.8300999999999999</v>
+        <v>0.9748</v>
       </c>
       <c r="L165" t="s">
         <v>15</v>
@@ -7716,16 +7716,16 @@
         <v>165</v>
       </c>
       <c r="C166">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="D166">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="E166">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F166">
-        <v>6939.78</v>
+        <v>6361.73</v>
       </c>
       <c r="G166">
         <v>0</v>
@@ -7848,16 +7848,16 @@
         <v>168</v>
       </c>
       <c r="C169">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="D169">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="E169">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F169">
-        <v>5541.77</v>
+        <v>5808.8</v>
       </c>
       <c r="G169">
         <v>2</v>
@@ -7869,10 +7869,10 @@
         <v>40</v>
       </c>
       <c r="J169">
-        <v>1.2631</v>
+        <v>1.2051</v>
       </c>
       <c r="K169">
-        <v>0.7218</v>
+        <v>0.6886</v>
       </c>
       <c r="L169" t="s">
         <v>15</v>
@@ -7892,10 +7892,10 @@
         <v>169</v>
       </c>
       <c r="C170">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D170">
-        <v>1829</v>
+        <v>1826</v>
       </c>
       <c r="E170">
         <v>90</v>
@@ -7983,13 +7983,13 @@
         <v>1156</v>
       </c>
       <c r="D172">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="E172">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F172">
-        <v>5541.77</v>
+        <v>5808.8</v>
       </c>
       <c r="G172">
         <v>3</v>
@@ -8001,10 +8001,10 @@
         <v>84</v>
       </c>
       <c r="J172">
-        <v>3.0315</v>
+        <v>2.8922</v>
       </c>
       <c r="K172">
-        <v>1.5158</v>
+        <v>1.4461</v>
       </c>
       <c r="L172" t="s">
         <v>15</v>
@@ -8071,13 +8071,13 @@
         <v>720</v>
       </c>
       <c r="D174">
-        <v>1830</v>
+        <v>1829</v>
       </c>
       <c r="E174">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F174">
-        <v>5808.8</v>
+        <v>5541.77</v>
       </c>
       <c r="G174">
         <v>2</v>
@@ -8089,10 +8089,10 @@
         <v>48</v>
       </c>
       <c r="J174">
-        <v>1.1018</v>
+        <v>1.1549</v>
       </c>
       <c r="K174">
-        <v>0.8263</v>
+        <v>0.8661</v>
       </c>
       <c r="L174" t="s">
         <v>15</v>
@@ -8112,31 +8112,31 @@
         <v>174</v>
       </c>
       <c r="C175">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="D175">
-        <v>1830</v>
+        <v>1817</v>
       </c>
       <c r="E175">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="F175">
-        <v>5808.8</v>
+        <v>6939.78</v>
       </c>
       <c r="G175">
         <v>2</v>
       </c>
       <c r="H175">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I175">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="J175">
-        <v>1.2567</v>
+        <v>1.124</v>
       </c>
       <c r="K175">
-        <v>0.6886</v>
+        <v>0.7349</v>
       </c>
       <c r="L175" t="s">
         <v>15</v>
@@ -8332,10 +8332,10 @@
         <v>179</v>
       </c>
       <c r="C180">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="D180">
-        <v>1938</v>
+        <v>1937</v>
       </c>
       <c r="E180">
         <v>84</v>
@@ -8508,31 +8508,31 @@
         <v>183</v>
       </c>
       <c r="C184">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D184">
         <v>1940</v>
       </c>
       <c r="E184">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F184">
-        <v>6647.61</v>
+        <v>6082.12</v>
       </c>
       <c r="G184">
         <v>2</v>
       </c>
       <c r="H184">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="I184">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J184">
-        <v>1.4893</v>
+        <v>1.7264</v>
       </c>
       <c r="K184">
-        <v>1.038</v>
+        <v>1.1838</v>
       </c>
       <c r="L184" t="s">
         <v>15</v>
@@ -8684,31 +8684,31 @@
         <v>187</v>
       </c>
       <c r="C188">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D188">
-        <v>1941</v>
+        <v>1935</v>
       </c>
       <c r="E188">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F188">
-        <v>6647.61</v>
+        <v>6939.78</v>
       </c>
       <c r="G188">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H188">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="I188">
         <v>21</v>
       </c>
       <c r="J188">
-        <v>0.5716</v>
+        <v>0.3026</v>
       </c>
       <c r="K188">
-        <v>0.3159</v>
+        <v>0.3026</v>
       </c>
       <c r="L188" t="s">
         <v>15</v>
@@ -8819,7 +8819,7 @@
         <v>861</v>
       </c>
       <c r="D191">
-        <v>1941</v>
+        <v>1940</v>
       </c>
       <c r="E191">
         <v>86</v>
@@ -8860,16 +8860,16 @@
         <v>191</v>
       </c>
       <c r="C192">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="D192">
-        <v>1943</v>
+        <v>1948</v>
       </c>
       <c r="E192">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F192">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G192">
         <v>0</v>
@@ -9039,13 +9039,13 @@
         <v>1600</v>
       </c>
       <c r="D196">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="E196">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F196">
-        <v>5808.8</v>
+        <v>5541.77</v>
       </c>
       <c r="G196">
         <v>2</v>
@@ -9057,10 +9057,10 @@
         <v>84</v>
       </c>
       <c r="J196">
-        <v>2.1691</v>
+        <v>2.2736</v>
       </c>
       <c r="K196">
-        <v>1.4461</v>
+        <v>1.5158</v>
       </c>
       <c r="L196" t="s">
         <v>15</v>
@@ -9124,10 +9124,10 @@
         <v>197</v>
       </c>
       <c r="C198">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="D198">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="E198">
         <v>94</v>
@@ -9435,13 +9435,13 @@
         <v>1751</v>
       </c>
       <c r="D205">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="E205">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F205">
-        <v>5808.8</v>
+        <v>5541.77</v>
       </c>
       <c r="G205">
         <v>2</v>
@@ -9453,10 +9453,10 @@
         <v>97</v>
       </c>
       <c r="J205">
-        <v>2.8405</v>
+        <v>2.9774</v>
       </c>
       <c r="K205">
-        <v>1.6699</v>
+        <v>1.7503</v>
       </c>
       <c r="L205" t="s">
         <v>15</v>
@@ -9476,31 +9476,31 @@
         <v>205</v>
       </c>
       <c r="C206">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="D206">
-        <v>2055</v>
+        <v>2047</v>
       </c>
       <c r="E206">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F206">
-        <v>6361.73</v>
+        <v>6939.78</v>
       </c>
       <c r="G206">
         <v>1</v>
       </c>
       <c r="H206">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I206">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J206">
-        <v>0.6288</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K206">
-        <v>0.6288</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L206" t="s">
         <v>15</v>
@@ -9564,31 +9564,31 @@
         <v>207</v>
       </c>
       <c r="C208">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D208">
         <v>2056</v>
       </c>
       <c r="E208">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F208">
-        <v>6647.61</v>
+        <v>6082.12</v>
       </c>
       <c r="G208">
         <v>2</v>
       </c>
       <c r="H208">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="I208">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J208">
-        <v>3.1289</v>
+        <v>3.5021</v>
       </c>
       <c r="K208">
-        <v>2.1963</v>
+        <v>2.4498</v>
       </c>
       <c r="L208" t="s">
         <v>15</v>
@@ -9608,31 +9608,31 @@
         <v>208</v>
       </c>
       <c r="C209">
-        <v>2362</v>
+        <v>2355</v>
       </c>
       <c r="D209">
-        <v>2165</v>
+        <v>2160</v>
       </c>
       <c r="E209">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F209">
-        <v>6082.12</v>
+        <v>6647.61</v>
       </c>
       <c r="G209">
         <v>1</v>
       </c>
       <c r="H209">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="I209">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J209">
-        <v>1.1345</v>
+        <v>1.0079</v>
       </c>
       <c r="K209">
-        <v>1.1345</v>
+        <v>1.0079</v>
       </c>
       <c r="L209" t="s">
         <v>15</v>
@@ -9652,16 +9652,16 @@
         <v>209</v>
       </c>
       <c r="C210">
-        <v>2207</v>
+        <v>2204</v>
       </c>
       <c r="D210">
-        <v>2166</v>
+        <v>2162</v>
       </c>
       <c r="E210">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F210">
-        <v>6082.12</v>
+        <v>6647.61</v>
       </c>
       <c r="G210">
         <v>0</v>
@@ -9696,10 +9696,10 @@
         <v>210</v>
       </c>
       <c r="C211">
-        <v>2056</v>
+        <v>2061</v>
       </c>
       <c r="D211">
-        <v>2167</v>
+        <v>2163</v>
       </c>
       <c r="E211">
         <v>88</v>
@@ -9708,16 +9708,16 @@
         <v>6082.12</v>
       </c>
       <c r="G211">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H211">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="I211">
         <v>59</v>
       </c>
       <c r="J211">
-        <v>1.7593</v>
+        <v>1.2331</v>
       </c>
       <c r="K211">
         <v>0.9701</v>
@@ -10403,7 +10403,7 @@
         <v>2373</v>
       </c>
       <c r="D227">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="E227">
         <v>90</v>
@@ -10415,16 +10415,16 @@
         <v>1</v>
       </c>
       <c r="H227">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="I227">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="J227">
-        <v>2.0278</v>
+        <v>2.1378</v>
       </c>
       <c r="K227">
-        <v>2.0278</v>
+        <v>2.1378</v>
       </c>
       <c r="L227" t="s">
         <v>15</v>
@@ -10488,31 +10488,31 @@
         <v>228</v>
       </c>
       <c r="C229">
-        <v>2068</v>
+        <v>2075</v>
       </c>
       <c r="D229">
-        <v>2288</v>
+        <v>2296</v>
       </c>
       <c r="E229">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F229">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G229">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H229">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="I229">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J229">
-        <v>1.6977</v>
+        <v>1.1282</v>
       </c>
       <c r="K229">
-        <v>0.9274</v>
+        <v>0.8424</v>
       </c>
       <c r="L229" t="s">
         <v>15</v>
@@ -10532,10 +10532,10 @@
         <v>229</v>
       </c>
       <c r="C230">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="D230">
-        <v>2288</v>
+        <v>2286</v>
       </c>
       <c r="E230">
         <v>88</v>
@@ -10667,28 +10667,28 @@
         <v>849</v>
       </c>
       <c r="D233">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="E233">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F233">
-        <v>6939.78</v>
+        <v>6082.12</v>
       </c>
       <c r="G233">
         <v>1</v>
       </c>
       <c r="H233">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I233">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J233">
-        <v>0.9943</v>
+        <v>1.1509</v>
       </c>
       <c r="K233">
-        <v>0.9943</v>
+        <v>1.1509</v>
       </c>
       <c r="L233" t="s">
         <v>15</v>
@@ -10840,31 +10840,31 @@
         <v>236</v>
       </c>
       <c r="C237">
-        <v>1764</v>
+        <v>1772</v>
       </c>
       <c r="D237">
-        <v>2289</v>
+        <v>2297</v>
       </c>
       <c r="E237">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F237">
-        <v>6361.73</v>
+        <v>6939.78</v>
       </c>
       <c r="G237">
         <v>2</v>
       </c>
       <c r="H237">
-        <v>147</v>
+        <v>98</v>
       </c>
       <c r="I237">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="J237">
-        <v>2.3107</v>
+        <v>1.4121</v>
       </c>
       <c r="K237">
-        <v>1.4933</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="L237" t="s">
         <v>15</v>
@@ -10884,16 +10884,16 @@
         <v>237</v>
       </c>
       <c r="C238">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="D238">
         <v>2289</v>
       </c>
       <c r="E238">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F238">
-        <v>6361.73</v>
+        <v>6082.12</v>
       </c>
       <c r="G238">
         <v>3</v>
@@ -10905,10 +10905,10 @@
         <v>61</v>
       </c>
       <c r="J238">
-        <v>1.9806</v>
+        <v>2.0716</v>
       </c>
       <c r="K238">
-        <v>0.9589</v>
+        <v>1.0029</v>
       </c>
       <c r="L238" t="s">
         <v>15</v>
@@ -11016,31 +11016,31 @@
         <v>240</v>
       </c>
       <c r="C241">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="D241">
-        <v>2401</v>
+        <v>2405</v>
       </c>
       <c r="E241">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F241">
-        <v>6361.73</v>
+        <v>6939.78</v>
       </c>
       <c r="G241">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H241">
-        <v>184</v>
+        <v>288</v>
       </c>
       <c r="I241">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J241">
-        <v>2.8923</v>
+        <v>4.15</v>
       </c>
       <c r="K241">
-        <v>1.0689</v>
+        <v>0.9654</v>
       </c>
       <c r="L241" t="s">
         <v>15</v>
@@ -11060,10 +11060,10 @@
         <v>241</v>
       </c>
       <c r="C242">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="D242">
-        <v>2407</v>
+        <v>2405</v>
       </c>
       <c r="E242">
         <v>90</v>
@@ -11236,31 +11236,31 @@
         <v>245</v>
       </c>
       <c r="C246">
-        <v>462</v>
+        <v>518</v>
       </c>
       <c r="D246">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="E246">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F246">
-        <v>5026.55</v>
+        <v>3848.45</v>
       </c>
       <c r="G246">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H246">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="I246">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J246">
-        <v>0</v>
+        <v>2.2866</v>
       </c>
       <c r="K246">
-        <v>0</v>
+        <v>1.0134</v>
       </c>
       <c r="L246" t="s">
         <v>15</v>
@@ -11720,16 +11720,16 @@
         <v>256</v>
       </c>
       <c r="C257">
-        <v>2325</v>
+        <v>2267</v>
       </c>
       <c r="D257">
-        <v>1308</v>
+        <v>1293</v>
       </c>
       <c r="E257">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F257">
-        <v>4300.84</v>
+        <v>4071.5</v>
       </c>
       <c r="G257">
         <v>0</v>
@@ -11750,7 +11750,7 @@
         <v>15</v>
       </c>
       <c r="M257" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N257">
         <v>0.2</v>
@@ -11829,10 +11829,10 @@
         <v>256</v>
       </c>
       <c r="C2">
-        <v>1.4761</v>
+        <v>1.6181</v>
       </c>
       <c r="D2">
-        <v>7.4948</v>
+        <v>11.0522</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -11859,7 +11859,7 @@
         <v>0</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Images_BGA/Results/Reports/PCBA2_03__inspection_report.xlsx
+++ b/Images_BGA/Results/Reports/PCBA2_03__inspection_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="28">
   <si>
     <t>image_name</t>
   </si>
@@ -430,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N257"/>
+  <dimension ref="A1:N256"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -1292,31 +1292,31 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="D20">
-        <v>908</v>
+        <v>926</v>
       </c>
       <c r="E20">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F20">
-        <v>6361.73</v>
+        <v>5808.8</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="H20">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I20">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J20">
-        <v>0.2987</v>
+        <v>0.5337</v>
       </c>
       <c r="K20">
-        <v>0.2987</v>
+        <v>0.5337</v>
       </c>
       <c r="L20" t="s">
         <v>15</v>
@@ -1427,28 +1427,28 @@
         <v>1160</v>
       </c>
       <c r="D23">
-        <v>910</v>
+        <v>928</v>
       </c>
       <c r="E23">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F23">
-        <v>6082.12</v>
+        <v>5541.77</v>
       </c>
       <c r="G23">
         <v>3</v>
       </c>
       <c r="H23">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="I23">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="J23">
-        <v>3.1568</v>
+        <v>3.0857</v>
       </c>
       <c r="K23">
-        <v>1.6935</v>
+        <v>1.9308</v>
       </c>
       <c r="L23" t="s">
         <v>15</v>
@@ -1908,31 +1908,31 @@
         <v>33</v>
       </c>
       <c r="C34">
-        <v>1558</v>
+        <v>1566</v>
       </c>
       <c r="D34">
-        <v>995</v>
+        <v>1012</v>
       </c>
       <c r="E34">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F34">
-        <v>6082.12</v>
+        <v>4778.36</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
       <c r="H34">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="I34">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="J34">
-        <v>1.562</v>
+        <v>2.2811</v>
       </c>
       <c r="K34">
-        <v>1.562</v>
+        <v>2.2811</v>
       </c>
       <c r="L34" t="s">
         <v>15</v>
@@ -11236,31 +11236,31 @@
         <v>245</v>
       </c>
       <c r="C246">
-        <v>518</v>
+        <v>539</v>
       </c>
       <c r="D246">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="E246">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="F246">
-        <v>3848.45</v>
+        <v>6939.78</v>
       </c>
       <c r="G246">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H246">
-        <v>88</v>
+        <v>131</v>
       </c>
       <c r="I246">
-        <v>39</v>
+        <v>111</v>
       </c>
       <c r="J246">
-        <v>2.2866</v>
+        <v>1.8877</v>
       </c>
       <c r="K246">
-        <v>1.0134</v>
+        <v>1.5995</v>
       </c>
       <c r="L246" t="s">
         <v>15</v>
@@ -11280,31 +11280,31 @@
         <v>246</v>
       </c>
       <c r="C247">
-        <v>539</v>
+        <v>1768</v>
       </c>
       <c r="D247">
         <v>2409</v>
       </c>
       <c r="E247">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F247">
-        <v>6939.78</v>
+        <v>6361.73</v>
       </c>
       <c r="G247">
         <v>2</v>
       </c>
       <c r="H247">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="I247">
-        <v>111</v>
+        <v>59</v>
       </c>
       <c r="J247">
-        <v>1.8877</v>
+        <v>1.399</v>
       </c>
       <c r="K247">
-        <v>1.5995</v>
+        <v>0.9274</v>
       </c>
       <c r="L247" t="s">
         <v>15</v>
@@ -11324,7 +11324,7 @@
         <v>247</v>
       </c>
       <c r="C248">
-        <v>1768</v>
+        <v>1922</v>
       </c>
       <c r="D248">
         <v>2409</v>
@@ -11339,16 +11339,16 @@
         <v>2</v>
       </c>
       <c r="H248">
-        <v>89</v>
+        <v>191</v>
       </c>
       <c r="I248">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="J248">
-        <v>1.399</v>
+        <v>3.0023</v>
       </c>
       <c r="K248">
-        <v>0.9274</v>
+        <v>1.5247</v>
       </c>
       <c r="L248" t="s">
         <v>15</v>
@@ -11368,31 +11368,31 @@
         <v>248</v>
       </c>
       <c r="C249">
-        <v>1922</v>
+        <v>692</v>
       </c>
       <c r="D249">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="E249">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F249">
-        <v>6361.73</v>
+        <v>6939.78</v>
       </c>
       <c r="G249">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H249">
-        <v>191</v>
+        <v>87</v>
       </c>
       <c r="I249">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="J249">
-        <v>3.0023</v>
+        <v>1.2536</v>
       </c>
       <c r="K249">
-        <v>1.5247</v>
+        <v>0.3602</v>
       </c>
       <c r="L249" t="s">
         <v>15</v>
@@ -11412,7 +11412,7 @@
         <v>249</v>
       </c>
       <c r="C250">
-        <v>692</v>
+        <v>845</v>
       </c>
       <c r="D250">
         <v>2410</v>
@@ -11424,19 +11424,19 @@
         <v>6939.78</v>
       </c>
       <c r="G250">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H250">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="I250">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="J250">
-        <v>1.2536</v>
+        <v>1.4266</v>
       </c>
       <c r="K250">
-        <v>0.3602</v>
+        <v>0.634</v>
       </c>
       <c r="L250" t="s">
         <v>15</v>
@@ -11456,31 +11456,31 @@
         <v>250</v>
       </c>
       <c r="C251">
-        <v>845</v>
+        <v>1614</v>
       </c>
       <c r="D251">
         <v>2410</v>
       </c>
       <c r="E251">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F251">
-        <v>6939.78</v>
+        <v>6361.73</v>
       </c>
       <c r="G251">
         <v>3</v>
       </c>
       <c r="H251">
-        <v>99</v>
+        <v>133</v>
       </c>
       <c r="I251">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J251">
-        <v>1.4266</v>
+        <v>2.0906</v>
       </c>
       <c r="K251">
-        <v>0.634</v>
+        <v>0.8174</v>
       </c>
       <c r="L251" t="s">
         <v>15</v>
@@ -11500,31 +11500,31 @@
         <v>251</v>
       </c>
       <c r="C252">
-        <v>1614</v>
+        <v>999</v>
       </c>
       <c r="D252">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="E252">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F252">
-        <v>6361.73</v>
+        <v>6939.78</v>
       </c>
       <c r="G252">
         <v>3</v>
       </c>
       <c r="H252">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="I252">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J252">
-        <v>2.0906</v>
+        <v>1.6715</v>
       </c>
       <c r="K252">
-        <v>0.8174</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="L252" t="s">
         <v>15</v>
@@ -11544,7 +11544,7 @@
         <v>252</v>
       </c>
       <c r="C253">
-        <v>999</v>
+        <v>1153</v>
       </c>
       <c r="D253">
         <v>2411</v>
@@ -11559,16 +11559,16 @@
         <v>3</v>
       </c>
       <c r="H253">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="I253">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="J253">
-        <v>1.6715</v>
+        <v>1.7868</v>
       </c>
       <c r="K253">
-        <v>0.7060999999999999</v>
+        <v>0.9366</v>
       </c>
       <c r="L253" t="s">
         <v>15</v>
@@ -11588,31 +11588,31 @@
         <v>253</v>
       </c>
       <c r="C254">
-        <v>1153</v>
+        <v>1307</v>
       </c>
       <c r="D254">
         <v>2411</v>
       </c>
       <c r="E254">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F254">
-        <v>6939.78</v>
+        <v>6647.61</v>
       </c>
       <c r="G254">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H254">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="I254">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="J254">
-        <v>1.7868</v>
+        <v>1.0681</v>
       </c>
       <c r="K254">
-        <v>0.9366</v>
+        <v>0.6468</v>
       </c>
       <c r="L254" t="s">
         <v>15</v>
@@ -11632,7 +11632,7 @@
         <v>254</v>
       </c>
       <c r="C255">
-        <v>1307</v>
+        <v>1461</v>
       </c>
       <c r="D255">
         <v>2411</v>
@@ -11647,16 +11647,16 @@
         <v>2</v>
       </c>
       <c r="H255">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I255">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J255">
-        <v>1.0681</v>
+        <v>1.1132</v>
       </c>
       <c r="K255">
-        <v>0.6468</v>
+        <v>0.5867</v>
       </c>
       <c r="L255" t="s">
         <v>15</v>
@@ -11676,31 +11676,31 @@
         <v>255</v>
       </c>
       <c r="C256">
-        <v>1461</v>
+        <v>2267</v>
       </c>
       <c r="D256">
-        <v>2411</v>
+        <v>1293</v>
       </c>
       <c r="E256">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="F256">
-        <v>6647.61</v>
+        <v>4071.5</v>
       </c>
       <c r="G256">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H256">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="I256">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J256">
-        <v>1.1132</v>
+        <v>0</v>
       </c>
       <c r="K256">
-        <v>0.5867</v>
+        <v>0</v>
       </c>
       <c r="L256" t="s">
         <v>15</v>
@@ -11709,50 +11709,6 @@
         <v>0</v>
       </c>
       <c r="N256">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="257" spans="1:14">
-      <c r="A257" t="s">
-        <v>14</v>
-      </c>
-      <c r="B257">
-        <v>256</v>
-      </c>
-      <c r="C257">
-        <v>2267</v>
-      </c>
-      <c r="D257">
-        <v>1293</v>
-      </c>
-      <c r="E257">
-        <v>72</v>
-      </c>
-      <c r="F257">
-        <v>4071.5</v>
-      </c>
-      <c r="G257">
-        <v>0</v>
-      </c>
-      <c r="H257">
-        <v>0</v>
-      </c>
-      <c r="I257">
-        <v>0</v>
-      </c>
-      <c r="J257">
-        <v>0</v>
-      </c>
-      <c r="K257">
-        <v>0</v>
-      </c>
-      <c r="L257" t="s">
-        <v>15</v>
-      </c>
-      <c r="M257" t="b">
-        <v>0</v>
-      </c>
-      <c r="N257">
         <v>0.2</v>
       </c>
     </row>
@@ -11826,10 +11782,10 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C2">
-        <v>1.6181</v>
+        <v>1.6189</v>
       </c>
       <c r="D2">
         <v>11.0522</v>
@@ -11850,7 +11806,7 @@
         <v>12</v>
       </c>
       <c r="J2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K2">
         <v>0</v>

--- a/Images_BGA/Results/Reports/PCBA2_03__inspection_report.xlsx
+++ b/Images_BGA/Results/Reports/PCBA2_03__inspection_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="28">
   <si>
     <t>image_name</t>
   </si>
@@ -430,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N256"/>
+  <dimension ref="A1:N257"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -632,16 +632,16 @@
         <v>4</v>
       </c>
       <c r="C5">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="D5">
-        <v>853</v>
+        <v>835</v>
       </c>
       <c r="E5">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F5">
-        <v>6082.12</v>
+        <v>5281.02</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -676,16 +676,16 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="D6">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="E6">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="F6">
-        <v>6939.78</v>
+        <v>5026.55</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -764,10 +764,10 @@
         <v>7</v>
       </c>
       <c r="C8">
-        <v>2195</v>
+        <v>2210</v>
       </c>
       <c r="D8">
-        <v>836</v>
+        <v>851</v>
       </c>
       <c r="E8">
         <v>84</v>
@@ -776,19 +776,19 @@
         <v>5541.77</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>648</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>11.693</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>11.693</v>
       </c>
       <c r="L8" t="s">
         <v>15</v>
@@ -811,28 +811,28 @@
         <v>1285</v>
       </c>
       <c r="D9">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="E9">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F9">
-        <v>6939.78</v>
+        <v>5281.02</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>612</v>
+        <v>438</v>
       </c>
       <c r="I9">
-        <v>564</v>
+        <v>438</v>
       </c>
       <c r="J9">
-        <v>8.8187</v>
+        <v>8.293900000000001</v>
       </c>
       <c r="K9">
-        <v>8.1271</v>
+        <v>8.293900000000001</v>
       </c>
       <c r="L9" t="s">
         <v>15</v>
@@ -852,10 +852,10 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="D10">
-        <v>838</v>
+        <v>861</v>
       </c>
       <c r="E10">
         <v>78</v>
@@ -864,19 +864,19 @@
         <v>4778.36</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>1.2557</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>1.2557</v>
+        <v>0</v>
       </c>
       <c r="L10" t="s">
         <v>15</v>
@@ -896,10 +896,10 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="D11">
-        <v>838</v>
+        <v>861</v>
       </c>
       <c r="E11">
         <v>82</v>
@@ -908,19 +908,19 @@
         <v>5281.02</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>1.5149</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>0.9657</v>
+        <v>0</v>
       </c>
       <c r="L11" t="s">
         <v>15</v>
@@ -943,28 +943,28 @@
         <v>1157</v>
       </c>
       <c r="D12">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="E12">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F12">
-        <v>6939.78</v>
+        <v>5541.77</v>
       </c>
       <c r="G12">
         <v>1</v>
       </c>
       <c r="H12">
-        <v>31</v>
+        <v>588</v>
       </c>
       <c r="I12">
-        <v>31</v>
+        <v>588</v>
       </c>
       <c r="J12">
-        <v>0.4467</v>
+        <v>10.6103</v>
       </c>
       <c r="K12">
-        <v>0.4467</v>
+        <v>10.6103</v>
       </c>
       <c r="L12" t="s">
         <v>15</v>
@@ -984,31 +984,31 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="D13">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="E13">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F13">
-        <v>4300.84</v>
+        <v>5281.02</v>
       </c>
       <c r="G13">
         <v>2</v>
       </c>
       <c r="H13">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="I13">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="J13">
-        <v>2.9064</v>
+        <v>2.2344</v>
       </c>
       <c r="K13">
-        <v>1.9531</v>
+        <v>1.4581</v>
       </c>
       <c r="L13" t="s">
         <v>15</v>
@@ -1028,31 +1028,31 @@
         <v>13</v>
       </c>
       <c r="C14">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D14">
         <v>837</v>
       </c>
       <c r="E14">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F14">
-        <v>4778.36</v>
+        <v>5026.55</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I14">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="J14">
-        <v>2.1765</v>
+        <v>1.9894</v>
       </c>
       <c r="K14">
-        <v>2.1765</v>
+        <v>1.9894</v>
       </c>
       <c r="L14" t="s">
         <v>15</v>
@@ -1075,28 +1075,28 @@
         <v>887</v>
       </c>
       <c r="D15">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="E15">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="F15">
-        <v>6939.78</v>
+        <v>5281.02</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15">
-        <v>767</v>
+        <v>529</v>
       </c>
       <c r="I15">
-        <v>767</v>
+        <v>529</v>
       </c>
       <c r="J15">
-        <v>11.0522</v>
+        <v>10.017</v>
       </c>
       <c r="K15">
-        <v>11.0522</v>
+        <v>10.017</v>
       </c>
       <c r="L15" t="s">
         <v>15</v>
@@ -1116,31 +1116,31 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D16">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E16">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F16">
-        <v>5026.55</v>
+        <v>4536.46</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>0.4377</v>
+        <v>0</v>
       </c>
       <c r="K16">
-        <v>0.4377</v>
+        <v>0</v>
       </c>
       <c r="L16" t="s">
         <v>15</v>
@@ -1204,10 +1204,10 @@
         <v>17</v>
       </c>
       <c r="C18">
-        <v>1990</v>
+        <v>1948</v>
       </c>
       <c r="D18">
-        <v>900</v>
+        <v>893</v>
       </c>
       <c r="E18">
         <v>74</v>
@@ -1216,19 +1216,19 @@
         <v>4300.84</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="I18">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J18">
-        <v>1.6973</v>
+        <v>2.1159</v>
       </c>
       <c r="K18">
-        <v>1.6973</v>
+        <v>1.6741</v>
       </c>
       <c r="L18" t="s">
         <v>15</v>
@@ -1248,10 +1248,10 @@
         <v>18</v>
       </c>
       <c r="C19">
-        <v>1875</v>
+        <v>1867</v>
       </c>
       <c r="D19">
-        <v>906</v>
+        <v>894</v>
       </c>
       <c r="E19">
         <v>76</v>
@@ -1263,16 +1263,16 @@
         <v>1</v>
       </c>
       <c r="H19">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="I19">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="J19">
-        <v>7.4948</v>
+        <v>7.4287</v>
       </c>
       <c r="K19">
-        <v>7.4948</v>
+        <v>7.4287</v>
       </c>
       <c r="L19" t="s">
         <v>15</v>
@@ -1336,10 +1336,10 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="D21">
-        <v>927</v>
+        <v>924</v>
       </c>
       <c r="E21">
         <v>76</v>
@@ -1380,10 +1380,10 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>2206</v>
+        <v>2219</v>
       </c>
       <c r="D22">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="E22">
         <v>80</v>
@@ -1468,10 +1468,10 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>1293</v>
+        <v>1284</v>
       </c>
       <c r="D24">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="E24">
         <v>86</v>
@@ -1480,19 +1480,19 @@
         <v>5808.8</v>
       </c>
       <c r="G24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="I24">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>1.2395</v>
+        <v>0</v>
       </c>
       <c r="K24">
-        <v>1.2395</v>
+        <v>0</v>
       </c>
       <c r="L24" t="s">
         <v>15</v>
@@ -1867,28 +1867,28 @@
         <v>1557</v>
       </c>
       <c r="D33">
-        <v>948</v>
+        <v>951</v>
       </c>
       <c r="E33">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F33">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
       <c r="H33">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="I33">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="J33">
-        <v>3.6625</v>
+        <v>3.5953</v>
       </c>
       <c r="K33">
-        <v>3.6625</v>
+        <v>3.5953</v>
       </c>
       <c r="L33" t="s">
         <v>15</v>
@@ -1952,16 +1952,16 @@
         <v>34</v>
       </c>
       <c r="C35">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="D35">
-        <v>999</v>
+        <v>1016</v>
       </c>
       <c r="E35">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F35">
-        <v>6082.12</v>
+        <v>5281.02</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -1996,31 +1996,31 @@
         <v>35</v>
       </c>
       <c r="C36">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="D36">
-        <v>1036</v>
+        <v>1017</v>
       </c>
       <c r="E36">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F36">
-        <v>6361.73</v>
+        <v>6082.12</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36">
-        <v>125</v>
+        <v>196</v>
       </c>
       <c r="I36">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="J36">
-        <v>1.9649</v>
+        <v>3.2226</v>
       </c>
       <c r="K36">
-        <v>1.9649</v>
+        <v>2.2525</v>
       </c>
       <c r="L36" t="s">
         <v>15</v>
@@ -2040,10 +2040,10 @@
         <v>36</v>
       </c>
       <c r="C37">
-        <v>1863</v>
+        <v>1836</v>
       </c>
       <c r="D37">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E37">
         <v>94</v>
@@ -2052,19 +2052,19 @@
         <v>6939.78</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H37">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="I37">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="J37">
-        <v>2.147</v>
+        <v>2.8099</v>
       </c>
       <c r="K37">
-        <v>2.147</v>
+        <v>2.3055</v>
       </c>
       <c r="L37" t="s">
         <v>15</v>
@@ -2084,31 +2084,31 @@
         <v>37</v>
       </c>
       <c r="C38">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D38">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="E38">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F38">
-        <v>3848.45</v>
+        <v>4300.84</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="I38">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>3.274</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>3.274</v>
+        <v>0</v>
       </c>
       <c r="L38" t="s">
         <v>15</v>
@@ -2128,31 +2128,31 @@
         <v>38</v>
       </c>
       <c r="C39">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="D39">
-        <v>1001</v>
+        <v>1019</v>
       </c>
       <c r="E39">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F39">
-        <v>6082.12</v>
+        <v>5808.8</v>
       </c>
       <c r="G39">
         <v>2</v>
       </c>
       <c r="H39">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I39">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J39">
-        <v>1.6113</v>
+        <v>1.6699</v>
       </c>
       <c r="K39">
-        <v>0.9701</v>
+        <v>1.0846</v>
       </c>
       <c r="L39" t="s">
         <v>15</v>
@@ -2172,10 +2172,10 @@
         <v>39</v>
       </c>
       <c r="C40">
-        <v>244</v>
+        <v>226</v>
       </c>
       <c r="D40">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="E40">
         <v>74</v>
@@ -2187,16 +2187,16 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="I40">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="J40">
-        <v>0.8835</v>
+        <v>0.5115</v>
       </c>
       <c r="K40">
-        <v>0.8835</v>
+        <v>0.5115</v>
       </c>
       <c r="L40" t="s">
         <v>15</v>
@@ -2348,10 +2348,10 @@
         <v>43</v>
       </c>
       <c r="C44">
-        <v>1294</v>
+        <v>1288</v>
       </c>
       <c r="D44">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="E44">
         <v>84</v>
@@ -2360,19 +2360,19 @@
         <v>5541.77</v>
       </c>
       <c r="G44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="I44">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="J44">
-        <v>0.794</v>
+        <v>1.0105</v>
       </c>
       <c r="K44">
-        <v>0.397</v>
+        <v>1.0105</v>
       </c>
       <c r="L44" t="s">
         <v>15</v>
@@ -2612,31 +2612,31 @@
         <v>49</v>
       </c>
       <c r="C50">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="D50">
-        <v>1090</v>
+        <v>1111</v>
       </c>
       <c r="E50">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F50">
-        <v>6647.61</v>
+        <v>5808.8</v>
       </c>
       <c r="G50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="I50">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J50">
-        <v>1.7299</v>
+        <v>1.6527</v>
       </c>
       <c r="K50">
-        <v>0.7822</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="L50" t="s">
         <v>15</v>
@@ -2656,16 +2656,16 @@
         <v>50</v>
       </c>
       <c r="C51">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="D51">
-        <v>1092</v>
+        <v>1111</v>
       </c>
       <c r="E51">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F51">
-        <v>6361.73</v>
+        <v>6082.12</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -2677,10 +2677,10 @@
         <v>30</v>
       </c>
       <c r="J51">
-        <v>0.4716</v>
+        <v>0.4932</v>
       </c>
       <c r="K51">
-        <v>0.4716</v>
+        <v>0.4932</v>
       </c>
       <c r="L51" t="s">
         <v>15</v>
@@ -2788,31 +2788,31 @@
         <v>53</v>
       </c>
       <c r="C54">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="D54">
-        <v>1096</v>
+        <v>1114</v>
       </c>
       <c r="E54">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F54">
-        <v>6647.61</v>
+        <v>6082.12</v>
       </c>
       <c r="G54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="I54">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J54">
-        <v>1.6848</v>
+        <v>2.2854</v>
       </c>
       <c r="K54">
-        <v>1.0831</v>
+        <v>1.2002</v>
       </c>
       <c r="L54" t="s">
         <v>15</v>
@@ -2832,10 +2832,10 @@
         <v>54</v>
       </c>
       <c r="C55">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="D55">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="E55">
         <v>86</v>
@@ -2876,7 +2876,7 @@
         <v>55</v>
       </c>
       <c r="C56">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D56">
         <v>1113</v>
@@ -2920,31 +2920,31 @@
         <v>56</v>
       </c>
       <c r="C57">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="D57">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="E57">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F57">
-        <v>6647.61</v>
+        <v>4778.36</v>
       </c>
       <c r="G57">
         <v>1</v>
       </c>
       <c r="H57">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="I57">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="J57">
-        <v>1.0681</v>
+        <v>1.2975</v>
       </c>
       <c r="K57">
-        <v>1.0681</v>
+        <v>1.2975</v>
       </c>
       <c r="L57" t="s">
         <v>15</v>
@@ -3231,28 +3231,28 @@
         <v>486</v>
       </c>
       <c r="D64">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="E64">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="F64">
-        <v>4300.84</v>
+        <v>5026.55</v>
       </c>
       <c r="G64">
         <v>1</v>
       </c>
       <c r="H64">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I64">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J64">
-        <v>0.9068000000000001</v>
+        <v>0.6764</v>
       </c>
       <c r="K64">
-        <v>0.9068000000000001</v>
+        <v>0.6764</v>
       </c>
       <c r="L64" t="s">
         <v>15</v>
@@ -3272,16 +3272,16 @@
         <v>64</v>
       </c>
       <c r="C65">
-        <v>2332</v>
+        <v>2274</v>
       </c>
       <c r="D65">
-        <v>1122</v>
+        <v>1136</v>
       </c>
       <c r="E65">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F65">
-        <v>5541.77</v>
+        <v>5026.55</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>65</v>
       </c>
       <c r="C66">
-        <v>1974</v>
+        <v>1977</v>
       </c>
       <c r="D66">
-        <v>1186</v>
+        <v>1205</v>
       </c>
       <c r="E66">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F66">
-        <v>6361.73</v>
+        <v>6082.12</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -3337,10 +3337,10 @@
         <v>132</v>
       </c>
       <c r="J66">
-        <v>2.0749</v>
+        <v>2.1703</v>
       </c>
       <c r="K66">
-        <v>2.0749</v>
+        <v>2.1703</v>
       </c>
       <c r="L66" t="s">
         <v>15</v>
@@ -3360,16 +3360,16 @@
         <v>66</v>
       </c>
       <c r="C67">
-        <v>2110</v>
+        <v>2113</v>
       </c>
       <c r="D67">
-        <v>1186</v>
+        <v>1205</v>
       </c>
       <c r="E67">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F67">
-        <v>6361.73</v>
+        <v>6082.12</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -3448,31 +3448,31 @@
         <v>68</v>
       </c>
       <c r="C69">
-        <v>1562</v>
+        <v>1571</v>
       </c>
       <c r="D69">
-        <v>1193</v>
+        <v>1207</v>
       </c>
       <c r="E69">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F69">
-        <v>6647.61</v>
+        <v>5541.77</v>
       </c>
       <c r="G69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H69">
-        <v>190</v>
+        <v>108</v>
       </c>
       <c r="I69">
-        <v>87</v>
+        <v>57</v>
       </c>
       <c r="J69">
-        <v>2.8582</v>
+        <v>1.9488</v>
       </c>
       <c r="K69">
-        <v>1.3087</v>
+        <v>1.0286</v>
       </c>
       <c r="L69" t="s">
         <v>15</v>
@@ -3536,7 +3536,7 @@
         <v>70</v>
       </c>
       <c r="C71">
-        <v>2297</v>
+        <v>2250</v>
       </c>
       <c r="D71">
         <v>1207</v>
@@ -3548,19 +3548,19 @@
         <v>4300.84</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I71">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J71">
-        <v>0</v>
+        <v>0.7673</v>
       </c>
       <c r="K71">
-        <v>0</v>
+        <v>0.7673</v>
       </c>
       <c r="L71" t="s">
         <v>15</v>
@@ -3800,16 +3800,16 @@
         <v>76</v>
       </c>
       <c r="C77">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D77">
         <v>1205</v>
       </c>
       <c r="E77">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F77">
-        <v>6647.61</v>
+        <v>6939.78</v>
       </c>
       <c r="G77">
         <v>2</v>
@@ -3821,10 +3821,10 @@
         <v>26</v>
       </c>
       <c r="J77">
-        <v>0.7371</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="K77">
-        <v>0.3911</v>
+        <v>0.3747</v>
       </c>
       <c r="L77" t="s">
         <v>15</v>
@@ -4328,7 +4328,7 @@
         <v>88</v>
       </c>
       <c r="C89">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="D89">
         <v>1309</v>
@@ -4460,7 +4460,7 @@
         <v>91</v>
       </c>
       <c r="C92">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="D92">
         <v>1310</v>
@@ -4475,16 +4475,16 @@
         <v>3</v>
       </c>
       <c r="H92">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="I92">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J92">
-        <v>4.0781</v>
+        <v>4.2586</v>
       </c>
       <c r="K92">
-        <v>1.9127</v>
+        <v>1.8767</v>
       </c>
       <c r="L92" t="s">
         <v>15</v>
@@ -4683,28 +4683,28 @@
         <v>2271</v>
       </c>
       <c r="D97">
-        <v>1379</v>
+        <v>1375</v>
       </c>
       <c r="E97">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F97">
-        <v>6939.78</v>
+        <v>5541.77</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H97">
-        <v>691</v>
+        <v>620</v>
       </c>
       <c r="I97">
-        <v>691</v>
+        <v>599</v>
       </c>
       <c r="J97">
-        <v>9.957100000000001</v>
+        <v>11.1878</v>
       </c>
       <c r="K97">
-        <v>9.957100000000001</v>
+        <v>10.8088</v>
       </c>
       <c r="L97" t="s">
         <v>15</v>
@@ -4900,10 +4900,10 @@
         <v>101</v>
       </c>
       <c r="C102">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="D102">
-        <v>1407</v>
+        <v>1389</v>
       </c>
       <c r="E102">
         <v>78</v>
@@ -5032,31 +5032,31 @@
         <v>104</v>
       </c>
       <c r="C105">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D105">
         <v>1409</v>
       </c>
       <c r="E105">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F105">
-        <v>4778.36</v>
+        <v>5281.02</v>
       </c>
       <c r="G105">
         <v>2</v>
       </c>
       <c r="H105">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I105">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="J105">
-        <v>1.6114</v>
+        <v>1.7042</v>
       </c>
       <c r="K105">
-        <v>0.9417</v>
+        <v>1.1551</v>
       </c>
       <c r="L105" t="s">
         <v>15</v>
@@ -5604,31 +5604,31 @@
         <v>117</v>
       </c>
       <c r="C118">
-        <v>1573</v>
+        <v>1578</v>
       </c>
       <c r="D118">
-        <v>1509</v>
+        <v>1506</v>
       </c>
       <c r="E118">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F118">
-        <v>6361.73</v>
+        <v>5541.77</v>
       </c>
       <c r="G118">
         <v>2</v>
       </c>
       <c r="H118">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="I118">
         <v>31</v>
       </c>
       <c r="J118">
-        <v>0.7702</v>
+        <v>0.9925</v>
       </c>
       <c r="K118">
-        <v>0.4873</v>
+        <v>0.5594</v>
       </c>
       <c r="L118" t="s">
         <v>15</v>
@@ -6399,7 +6399,7 @@
         <v>293</v>
       </c>
       <c r="D136">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="E136">
         <v>90</v>
@@ -7144,31 +7144,31 @@
         <v>152</v>
       </c>
       <c r="C153">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="D153">
         <v>1721</v>
       </c>
       <c r="E153">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="F153">
-        <v>5281.02</v>
+        <v>5808.8</v>
       </c>
       <c r="G153">
         <v>1</v>
       </c>
       <c r="H153">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I153">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J153">
-        <v>0.4734</v>
+        <v>0.396</v>
       </c>
       <c r="K153">
-        <v>0.4734</v>
+        <v>0.396</v>
       </c>
       <c r="L153" t="s">
         <v>15</v>
@@ -7408,31 +7408,31 @@
         <v>158</v>
       </c>
       <c r="C159">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="D159">
         <v>1730</v>
       </c>
       <c r="E159">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F159">
-        <v>6939.78</v>
+        <v>6082.12</v>
       </c>
       <c r="G159">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H159">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="I159">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J159">
-        <v>1.4266</v>
+        <v>2.2361</v>
       </c>
       <c r="K159">
-        <v>0.7349</v>
+        <v>0.8878</v>
       </c>
       <c r="L159" t="s">
         <v>15</v>
@@ -7584,31 +7584,31 @@
         <v>162</v>
       </c>
       <c r="C163">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="D163">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="E163">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F163">
-        <v>6939.78</v>
+        <v>5541.77</v>
       </c>
       <c r="G163">
         <v>2</v>
       </c>
       <c r="H163">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I163">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J163">
-        <v>1.2681</v>
+        <v>1.7143</v>
       </c>
       <c r="K163">
-        <v>0.7925</v>
+        <v>1.0466</v>
       </c>
       <c r="L163" t="s">
         <v>15</v>
@@ -7854,25 +7854,25 @@
         <v>1826</v>
       </c>
       <c r="E169">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F169">
-        <v>5808.8</v>
+        <v>6082.12</v>
       </c>
       <c r="G169">
         <v>2</v>
       </c>
       <c r="H169">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="I169">
         <v>40</v>
       </c>
       <c r="J169">
-        <v>1.2051</v>
+        <v>1.118</v>
       </c>
       <c r="K169">
-        <v>0.6886</v>
+        <v>0.6577</v>
       </c>
       <c r="L169" t="s">
         <v>15</v>
@@ -7986,25 +7986,25 @@
         <v>1828</v>
       </c>
       <c r="E172">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F172">
-        <v>5808.8</v>
+        <v>6082.12</v>
       </c>
       <c r="G172">
         <v>3</v>
       </c>
       <c r="H172">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="I172">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J172">
-        <v>2.8922</v>
+        <v>2.6964</v>
       </c>
       <c r="K172">
-        <v>1.4461</v>
+        <v>1.3482</v>
       </c>
       <c r="L172" t="s">
         <v>15</v>
@@ -8112,31 +8112,31 @@
         <v>174</v>
       </c>
       <c r="C175">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="D175">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="E175">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F175">
-        <v>6939.78</v>
+        <v>5808.8</v>
       </c>
       <c r="G175">
         <v>2</v>
       </c>
       <c r="H175">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="I175">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J175">
-        <v>1.124</v>
+        <v>1.4977</v>
       </c>
       <c r="K175">
-        <v>0.7349</v>
+        <v>0.9296</v>
       </c>
       <c r="L175" t="s">
         <v>15</v>
@@ -8156,10 +8156,10 @@
         <v>175</v>
       </c>
       <c r="C176">
-        <v>1447</v>
+        <v>1452</v>
       </c>
       <c r="D176">
-        <v>1830</v>
+        <v>1816</v>
       </c>
       <c r="E176">
         <v>86</v>
@@ -8168,19 +8168,19 @@
         <v>5808.8</v>
       </c>
       <c r="G176">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H176">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I176">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J176">
-        <v>0.3443</v>
+        <v>0.723</v>
       </c>
       <c r="K176">
-        <v>0.3443</v>
+        <v>0.3787</v>
       </c>
       <c r="L176" t="s">
         <v>15</v>
@@ -8816,10 +8816,10 @@
         <v>190</v>
       </c>
       <c r="C191">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D191">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="E191">
         <v>86</v>
@@ -9124,10 +9124,10 @@
         <v>197</v>
       </c>
       <c r="C198">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D198">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="E198">
         <v>94</v>
@@ -10312,10 +10312,10 @@
         <v>224</v>
       </c>
       <c r="C225">
-        <v>565</v>
+        <v>531</v>
       </c>
       <c r="D225">
-        <v>2283</v>
+        <v>2277</v>
       </c>
       <c r="E225">
         <v>78</v>
@@ -10324,19 +10324,19 @@
         <v>4778.36</v>
       </c>
       <c r="G225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H225">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="I225">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="J225">
-        <v>1.4022</v>
+        <v>0</v>
       </c>
       <c r="K225">
-        <v>1.4022</v>
+        <v>0</v>
       </c>
       <c r="L225" t="s">
         <v>15</v>
@@ -11019,28 +11019,28 @@
         <v>81</v>
       </c>
       <c r="D241">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="E241">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F241">
-        <v>6939.78</v>
+        <v>6361.73</v>
       </c>
       <c r="G241">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H241">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="I241">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J241">
-        <v>4.15</v>
+        <v>4.1184</v>
       </c>
       <c r="K241">
-        <v>0.9654</v>
+        <v>1.0689</v>
       </c>
       <c r="L241" t="s">
         <v>15</v>
@@ -11148,10 +11148,10 @@
         <v>243</v>
       </c>
       <c r="C244">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="D244">
-        <v>2408</v>
+        <v>2413</v>
       </c>
       <c r="E244">
         <v>94</v>
@@ -11236,31 +11236,31 @@
         <v>245</v>
       </c>
       <c r="C246">
-        <v>539</v>
+        <v>462</v>
       </c>
       <c r="D246">
         <v>2409</v>
       </c>
       <c r="E246">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="F246">
-        <v>6939.78</v>
+        <v>5026.55</v>
       </c>
       <c r="G246">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H246">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="I246">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="J246">
-        <v>1.8877</v>
+        <v>0</v>
       </c>
       <c r="K246">
-        <v>1.5995</v>
+        <v>0</v>
       </c>
       <c r="L246" t="s">
         <v>15</v>
@@ -11280,31 +11280,31 @@
         <v>246</v>
       </c>
       <c r="C247">
-        <v>1768</v>
+        <v>539</v>
       </c>
       <c r="D247">
         <v>2409</v>
       </c>
       <c r="E247">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F247">
-        <v>6361.73</v>
+        <v>6939.78</v>
       </c>
       <c r="G247">
         <v>2</v>
       </c>
       <c r="H247">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="I247">
-        <v>59</v>
+        <v>111</v>
       </c>
       <c r="J247">
-        <v>1.399</v>
+        <v>1.8877</v>
       </c>
       <c r="K247">
-        <v>0.9274</v>
+        <v>1.5995</v>
       </c>
       <c r="L247" t="s">
         <v>15</v>
@@ -11324,7 +11324,7 @@
         <v>247</v>
       </c>
       <c r="C248">
-        <v>1922</v>
+        <v>1768</v>
       </c>
       <c r="D248">
         <v>2409</v>
@@ -11339,16 +11339,16 @@
         <v>2</v>
       </c>
       <c r="H248">
-        <v>191</v>
+        <v>89</v>
       </c>
       <c r="I248">
-        <v>97</v>
+        <v>59</v>
       </c>
       <c r="J248">
-        <v>3.0023</v>
+        <v>1.399</v>
       </c>
       <c r="K248">
-        <v>1.5247</v>
+        <v>0.9274</v>
       </c>
       <c r="L248" t="s">
         <v>15</v>
@@ -11368,31 +11368,31 @@
         <v>248</v>
       </c>
       <c r="C249">
-        <v>692</v>
+        <v>1922</v>
       </c>
       <c r="D249">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="E249">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F249">
-        <v>6939.78</v>
+        <v>6361.73</v>
       </c>
       <c r="G249">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H249">
-        <v>87</v>
+        <v>191</v>
       </c>
       <c r="I249">
-        <v>25</v>
+        <v>97</v>
       </c>
       <c r="J249">
-        <v>1.2536</v>
+        <v>3.0023</v>
       </c>
       <c r="K249">
-        <v>0.3602</v>
+        <v>1.5247</v>
       </c>
       <c r="L249" t="s">
         <v>15</v>
@@ -11412,7 +11412,7 @@
         <v>249</v>
       </c>
       <c r="C250">
-        <v>845</v>
+        <v>692</v>
       </c>
       <c r="D250">
         <v>2410</v>
@@ -11424,19 +11424,19 @@
         <v>6939.78</v>
       </c>
       <c r="G250">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H250">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="I250">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="J250">
-        <v>1.4266</v>
+        <v>1.2536</v>
       </c>
       <c r="K250">
-        <v>0.634</v>
+        <v>0.3602</v>
       </c>
       <c r="L250" t="s">
         <v>15</v>
@@ -11456,31 +11456,31 @@
         <v>250</v>
       </c>
       <c r="C251">
-        <v>1614</v>
+        <v>845</v>
       </c>
       <c r="D251">
         <v>2410</v>
       </c>
       <c r="E251">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F251">
-        <v>6361.73</v>
+        <v>6939.78</v>
       </c>
       <c r="G251">
         <v>3</v>
       </c>
       <c r="H251">
-        <v>133</v>
+        <v>99</v>
       </c>
       <c r="I251">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="J251">
-        <v>2.0906</v>
+        <v>1.4266</v>
       </c>
       <c r="K251">
-        <v>0.8174</v>
+        <v>0.634</v>
       </c>
       <c r="L251" t="s">
         <v>15</v>
@@ -11500,31 +11500,31 @@
         <v>251</v>
       </c>
       <c r="C252">
-        <v>999</v>
+        <v>1614</v>
       </c>
       <c r="D252">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="E252">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F252">
-        <v>6939.78</v>
+        <v>6361.73</v>
       </c>
       <c r="G252">
         <v>3</v>
       </c>
       <c r="H252">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="I252">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J252">
-        <v>1.6715</v>
+        <v>2.0906</v>
       </c>
       <c r="K252">
-        <v>0.7060999999999999</v>
+        <v>0.8174</v>
       </c>
       <c r="L252" t="s">
         <v>15</v>
@@ -11544,7 +11544,7 @@
         <v>252</v>
       </c>
       <c r="C253">
-        <v>1153</v>
+        <v>999</v>
       </c>
       <c r="D253">
         <v>2411</v>
@@ -11559,16 +11559,16 @@
         <v>3</v>
       </c>
       <c r="H253">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="I253">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="J253">
-        <v>1.7868</v>
+        <v>1.6715</v>
       </c>
       <c r="K253">
-        <v>0.9366</v>
+        <v>0.7060999999999999</v>
       </c>
       <c r="L253" t="s">
         <v>15</v>
@@ -11588,31 +11588,31 @@
         <v>253</v>
       </c>
       <c r="C254">
-        <v>1307</v>
+        <v>1153</v>
       </c>
       <c r="D254">
         <v>2411</v>
       </c>
       <c r="E254">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F254">
-        <v>6647.61</v>
+        <v>6939.78</v>
       </c>
       <c r="G254">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H254">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="I254">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="J254">
-        <v>1.0681</v>
+        <v>1.7868</v>
       </c>
       <c r="K254">
-        <v>0.6468</v>
+        <v>0.9366</v>
       </c>
       <c r="L254" t="s">
         <v>15</v>
@@ -11632,7 +11632,7 @@
         <v>254</v>
       </c>
       <c r="C255">
-        <v>1461</v>
+        <v>1307</v>
       </c>
       <c r="D255">
         <v>2411</v>
@@ -11647,16 +11647,16 @@
         <v>2</v>
       </c>
       <c r="H255">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I255">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J255">
-        <v>1.1132</v>
+        <v>1.0681</v>
       </c>
       <c r="K255">
-        <v>0.5867</v>
+        <v>0.6468</v>
       </c>
       <c r="L255" t="s">
         <v>15</v>
@@ -11676,31 +11676,31 @@
         <v>255</v>
       </c>
       <c r="C256">
-        <v>2267</v>
+        <v>1461</v>
       </c>
       <c r="D256">
-        <v>1293</v>
+        <v>2411</v>
       </c>
       <c r="E256">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="F256">
-        <v>4071.5</v>
+        <v>6647.61</v>
       </c>
       <c r="G256">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H256">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="I256">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="J256">
-        <v>0</v>
+        <v>1.1132</v>
       </c>
       <c r="K256">
-        <v>0</v>
+        <v>0.5867</v>
       </c>
       <c r="L256" t="s">
         <v>15</v>
@@ -11709,6 +11709,50 @@
         <v>0</v>
       </c>
       <c r="N256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:14">
+      <c r="A257" t="s">
+        <v>14</v>
+      </c>
+      <c r="B257">
+        <v>256</v>
+      </c>
+      <c r="C257">
+        <v>2263</v>
+      </c>
+      <c r="D257">
+        <v>1289</v>
+      </c>
+      <c r="E257">
+        <v>80</v>
+      </c>
+      <c r="F257">
+        <v>5026.55</v>
+      </c>
+      <c r="G257">
+        <v>0</v>
+      </c>
+      <c r="H257">
+        <v>0</v>
+      </c>
+      <c r="I257">
+        <v>0</v>
+      </c>
+      <c r="J257">
+        <v>0</v>
+      </c>
+      <c r="K257">
+        <v>0</v>
+      </c>
+      <c r="L257" t="s">
+        <v>15</v>
+      </c>
+      <c r="M257" t="b">
+        <v>0</v>
+      </c>
+      <c r="N257">
         <v>0.2</v>
       </c>
     </row>
@@ -11782,13 +11826,13 @@
         <v>14</v>
       </c>
       <c r="B2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C2">
-        <v>1.6189</v>
+        <v>1.676</v>
       </c>
       <c r="D2">
-        <v>11.0522</v>
+        <v>11.693</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -11806,7 +11850,7 @@
         <v>12</v>
       </c>
       <c r="J2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K2">
         <v>0</v>
